--- a/word-monitor-sub-domain/report/history/keyword-table-20260713-174447.xlsx
+++ b/word-monitor-sub-domain/report/history/keyword-table-20260713-174447.xlsx
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>378</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -734,9 +734,7 @@
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="n"/>
       <c r="I2" s="7" t="n"/>
-      <c r="J2" s="8" t="n">
-        <v>68.8</v>
-      </c>
+      <c r="J2" s="8" t="n"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
     </row>
@@ -758,9 +756,7 @@
       <c r="G3" s="6" t="n"/>
       <c r="H3" s="7" t="n"/>
       <c r="I3" s="7" t="n"/>
-      <c r="J3" s="8" t="n">
-        <v>70.09999999999999</v>
-      </c>
+      <c r="J3" s="8" t="n"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
     </row>
@@ -782,9 +778,7 @@
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
-      <c r="J4" s="8" t="n">
-        <v>41.9</v>
-      </c>
+      <c r="J4" s="8" t="n"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
     </row>
@@ -806,9 +800,7 @@
       <c r="G5" s="6" t="n"/>
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
-      <c r="J5" s="8" t="n">
-        <v>58</v>
-      </c>
+      <c r="J5" s="8" t="n"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
     </row>
@@ -831,9 +823,7 @@
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
-      <c r="J6" s="8" t="n">
-        <v>46.7</v>
-      </c>
+      <c r="J6" s="8" t="n"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
     </row>
@@ -855,9 +845,7 @@
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
-      <c r="J7" s="8" t="n">
-        <v>48.7</v>
-      </c>
+      <c r="J7" s="8" t="n"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
     </row>
@@ -879,9 +867,7 @@
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
-      <c r="J8" s="8" t="n">
-        <v>40.9</v>
-      </c>
+      <c r="J8" s="8" t="n"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
     </row>
@@ -903,9 +889,7 @@
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
-      <c r="J9" s="8" t="n">
-        <v>31.3</v>
-      </c>
+      <c r="J9" s="8" t="n"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
     </row>
@@ -927,9 +911,7 @@
       <c r="G10" s="6" t="n"/>
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
-      <c r="J10" s="8" t="n">
-        <v>54.4</v>
-      </c>
+      <c r="J10" s="8" t="n"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
     </row>
@@ -951,9 +933,7 @@
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
-      <c r="J11" s="8" t="n">
-        <v>39.9</v>
-      </c>
+      <c r="J11" s="8" t="n"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
     </row>
@@ -975,9 +955,7 @@
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
-      <c r="J12" s="8" t="n">
-        <v>62.6</v>
-      </c>
+      <c r="J12" s="8" t="n"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
     </row>
@@ -999,9 +977,7 @@
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="7" t="n"/>
       <c r="I13" s="7" t="n"/>
-      <c r="J13" s="8" t="n">
-        <v>82.3</v>
-      </c>
+      <c r="J13" s="8" t="n"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
     </row>
@@ -1023,9 +999,7 @@
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n"/>
-      <c r="J14" s="8" t="n">
-        <v>36.7</v>
-      </c>
+      <c r="J14" s="8" t="n"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
     </row>
@@ -1047,9 +1021,7 @@
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
-      <c r="J15" s="8" t="n">
-        <v>74.7</v>
-      </c>
+      <c r="J15" s="8" t="n"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
     </row>
@@ -1071,9 +1043,7 @@
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n"/>
-      <c r="J16" s="8" t="n">
-        <v>52.4</v>
-      </c>
+      <c r="J16" s="8" t="n"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
     </row>
@@ -1095,9 +1065,7 @@
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="7" t="n"/>
       <c r="I17" s="7" t="n"/>
-      <c r="J17" s="8" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="J17" s="8" t="n"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
     </row>
@@ -1119,9 +1087,7 @@
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n"/>
-      <c r="J18" s="8" t="n">
-        <v>55.3</v>
-      </c>
+      <c r="J18" s="8" t="n"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
     </row>
@@ -1143,9 +1109,7 @@
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="7" t="n"/>
       <c r="I19" s="7" t="n"/>
-      <c r="J19" s="8" t="n">
-        <v>48.9</v>
-      </c>
+      <c r="J19" s="8" t="n"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
     </row>
@@ -1167,9 +1131,7 @@
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n"/>
-      <c r="J20" s="8" t="n">
-        <v>55.4</v>
-      </c>
+      <c r="J20" s="8" t="n"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
     </row>
@@ -1191,9 +1153,7 @@
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
-      <c r="J21" s="8" t="n">
-        <v>43.1</v>
-      </c>
+      <c r="J21" s="8" t="n"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
     </row>
@@ -1215,9 +1175,7 @@
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n"/>
-      <c r="J22" s="8" t="n">
-        <v>70.8</v>
-      </c>
+      <c r="J22" s="8" t="n"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
     </row>
@@ -1239,9 +1197,7 @@
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="7" t="n"/>
       <c r="I23" s="7" t="n"/>
-      <c r="J23" s="8" t="n">
-        <v>18.3</v>
-      </c>
+      <c r="J23" s="8" t="n"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
     </row>
@@ -1263,9 +1219,7 @@
       <c r="G24" s="6" t="n"/>
       <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n"/>
-      <c r="J24" s="8" t="n">
-        <v>54.8</v>
-      </c>
+      <c r="J24" s="8" t="n"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
     </row>
@@ -1287,9 +1241,7 @@
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="7" t="n"/>
       <c r="I25" s="7" t="n"/>
-      <c r="J25" s="8" t="n">
-        <v>42.6</v>
-      </c>
+      <c r="J25" s="8" t="n"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
     </row>
@@ -1311,9 +1263,7 @@
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
-      <c r="J26" s="8" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="J26" s="8" t="n"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
     </row>
@@ -1335,9 +1285,7 @@
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
-      <c r="J27" s="8" t="n">
-        <v>43.6</v>
-      </c>
+      <c r="J27" s="8" t="n"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
     </row>
@@ -1359,9 +1307,7 @@
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
-      <c r="J28" s="8" t="n">
-        <v>47.4</v>
-      </c>
+      <c r="J28" s="8" t="n"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
     </row>
@@ -1383,9 +1329,7 @@
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="7" t="n"/>
       <c r="I29" s="7" t="n"/>
-      <c r="J29" s="8" t="n">
-        <v>29.6</v>
-      </c>
+      <c r="J29" s="8" t="n"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
     </row>
@@ -1407,9 +1351,7 @@
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="n"/>
       <c r="I30" s="7" t="n"/>
-      <c r="J30" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="J30" s="8" t="n"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
     </row>
@@ -1431,9 +1373,7 @@
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
-      <c r="J31" s="8" t="n">
-        <v>33</v>
-      </c>
+      <c r="J31" s="8" t="n"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
     </row>
@@ -1455,9 +1395,7 @@
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="n"/>
       <c r="I32" s="7" t="n"/>
-      <c r="J32" s="8" t="n">
-        <v>30.1</v>
-      </c>
+      <c r="J32" s="8" t="n"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
     </row>
@@ -1479,9 +1417,7 @@
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="n"/>
-      <c r="J33" s="8" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="J33" s="8" t="n"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
     </row>
@@ -1503,9 +1439,7 @@
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="7" t="n"/>
       <c r="I34" s="7" t="n"/>
-      <c r="J34" s="8" t="n">
-        <v>61.6</v>
-      </c>
+      <c r="J34" s="8" t="n"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
     </row>
@@ -1527,9 +1461,7 @@
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="7" t="n"/>
-      <c r="J35" s="8" t="n">
-        <v>62.2</v>
-      </c>
+      <c r="J35" s="8" t="n"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
     </row>
@@ -1551,9 +1483,7 @@
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="7" t="n"/>
       <c r="I36" s="7" t="n"/>
-      <c r="J36" s="8" t="n">
-        <v>67.7</v>
-      </c>
+      <c r="J36" s="8" t="n"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
     </row>
@@ -1575,9 +1505,7 @@
       <c r="G37" s="6" t="n"/>
       <c r="H37" s="7" t="n"/>
       <c r="I37" s="7" t="n"/>
-      <c r="J37" s="8" t="n">
-        <v>66.2</v>
-      </c>
+      <c r="J37" s="8" t="n"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
     </row>
@@ -1599,9 +1527,7 @@
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="7" t="n"/>
       <c r="I38" s="7" t="n"/>
-      <c r="J38" s="8" t="n">
-        <v>17.3</v>
-      </c>
+      <c r="J38" s="8" t="n"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
     </row>
@@ -1623,9 +1549,7 @@
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="7" t="n"/>
-      <c r="J39" s="8" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="J39" s="8" t="n"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
     </row>
@@ -1647,9 +1571,7 @@
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="7" t="n"/>
-      <c r="J40" s="8" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="J40" s="8" t="n"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
     </row>
@@ -1671,9 +1593,7 @@
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="7" t="n"/>
       <c r="I41" s="7" t="n"/>
-      <c r="J41" s="8" t="n">
-        <v>77.7</v>
-      </c>
+      <c r="J41" s="8" t="n"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
     </row>
@@ -1695,9 +1615,7 @@
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="n"/>
       <c r="I42" s="7" t="n"/>
-      <c r="J42" s="8" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="J42" s="8" t="n"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
     </row>
@@ -1719,9 +1637,7 @@
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="7" t="n"/>
-      <c r="J43" s="8" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="J43" s="8" t="n"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
     </row>
@@ -1743,9 +1659,7 @@
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="7" t="n"/>
       <c r="I44" s="7" t="n"/>
-      <c r="J44" s="8" t="n">
-        <v>34.6</v>
-      </c>
+      <c r="J44" s="8" t="n"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
     </row>
@@ -1767,9 +1681,7 @@
       <c r="G45" s="6" t="n"/>
       <c r="H45" s="7" t="n"/>
       <c r="I45" s="7" t="n"/>
-      <c r="J45" s="8" t="n">
-        <v>13</v>
-      </c>
+      <c r="J45" s="8" t="n"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
     </row>
@@ -1791,9 +1703,7 @@
       <c r="G46" s="6" t="n"/>
       <c r="H46" s="7" t="n"/>
       <c r="I46" s="7" t="n"/>
-      <c r="J46" s="8" t="n">
-        <v>36.3</v>
-      </c>
+      <c r="J46" s="8" t="n"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
     </row>
@@ -1816,9 +1726,7 @@
       <c r="G47" s="6" t="n"/>
       <c r="H47" s="7" t="n"/>
       <c r="I47" s="7" t="n"/>
-      <c r="J47" s="8" t="n">
-        <v>65.2</v>
-      </c>
+      <c r="J47" s="8" t="n"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
     </row>
@@ -1840,9 +1748,7 @@
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="7" t="n"/>
       <c r="I48" s="7" t="n"/>
-      <c r="J48" s="8" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="J48" s="8" t="n"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
     </row>
@@ -1864,9 +1770,7 @@
       <c r="G49" s="6" t="n"/>
       <c r="H49" s="7" t="n"/>
       <c r="I49" s="7" t="n"/>
-      <c r="J49" s="8" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="J49" s="8" t="n"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
     </row>
